--- a/resources/Marks/2026/even/Computational Astrophysics.xlsx
+++ b/resources/Marks/2026/even/Computational Astrophysics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Computational Astrophysics/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1899" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EB36330-6250-4A62-B6F0-0E02B31D1787}"/>
+  <xr:revisionPtr revIDLastSave="1905" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74388FF3-0FF2-4B9E-B496-7EB98FFD9410}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marksheet" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="117">
   <si>
     <t>Final Marks</t>
   </si>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t>CIA</t>
-  </si>
-  <si>
-    <t>Composite Marks</t>
   </si>
   <si>
     <t>Max</t>
@@ -669,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -785,21 +782,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -809,17 +791,8 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -833,8 +806,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1163,97 +1148,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="49"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="55"/>
       <c r="R1" s="33"/>
     </row>
     <row r="2" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="49"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="55"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:20" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59" t="s">
+      <c r="C3" s="50"/>
+      <c r="D3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="59" t="s">
+      <c r="H3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q3" s="59" t="s">
+      <c r="P3" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="51" t="s">
         <v>12</v>
       </c>
       <c r="S3" s="1" t="s">
@@ -1326,35 +1311,35 @@
       <c r="B5" s="12">
         <v>590010833</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="56">
+      <c r="C5" s="49"/>
+      <c r="D5" s="12">
         <f>'Assignment 1'!AG6/10</f>
         <v>14.4</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="12">
         <f>('Quiz 1'!N6/10)*3</f>
         <v>12</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="12">
         <f>'Class Test 1'!O6/2</f>
         <v>10</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
       <c r="I5" s="26"/>
-      <c r="J5" s="56">
+      <c r="J5" s="12">
         <f t="shared" ref="J5:J16" si="0">SUM(D5:I5)</f>
         <v>36.4</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="12">
         <f t="shared" ref="K5:K16" si="1">J5/2</f>
         <v>18.2</v>
       </c>
-      <c r="L5" s="54"/>
-      <c r="M5" s="55"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="18"/>
       <c r="N5" s="18"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="61">
+      <c r="O5" s="29"/>
+      <c r="P5" s="5">
         <f t="shared" ref="P5:P16" si="2">SUM(K5,L5,O5)</f>
         <v>18.2</v>
       </c>
@@ -1373,35 +1358,35 @@
       <c r="B6" s="12">
         <v>590010853</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="56">
+      <c r="C6" s="49"/>
+      <c r="D6" s="12">
         <f>'Assignment 1'!AG7/10</f>
         <v>14.3</v>
       </c>
-      <c r="E6" s="56">
+      <c r="E6" s="12">
         <f>('Quiz 1'!N7/10)*3</f>
         <v>15</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="12">
         <f>'Class Test 1'!O7/2</f>
         <v>16.5</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
       <c r="I6" s="26"/>
-      <c r="J6" s="56">
+      <c r="J6" s="12">
         <f t="shared" si="0"/>
         <v>45.8</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="12">
         <f t="shared" si="1"/>
         <v>22.9</v>
       </c>
-      <c r="L6" s="54"/>
-      <c r="M6" s="55"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="18"/>
       <c r="N6" s="18"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="61">
+      <c r="O6" s="29"/>
+      <c r="P6" s="5">
         <f t="shared" si="2"/>
         <v>22.9</v>
       </c>
@@ -1420,35 +1405,35 @@
       <c r="B7" s="12">
         <v>590011314</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="56">
+      <c r="C7" s="49"/>
+      <c r="D7" s="12">
         <f>'Assignment 1'!AG8/10</f>
         <v>14.8</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="12">
         <f>('Quiz 1'!N8/10)*3</f>
         <v>14.100000000000001</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="12">
         <f>'Class Test 1'!O8/2</f>
         <v>16.5</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
-      <c r="J7" s="56">
+      <c r="J7" s="12">
         <f t="shared" si="0"/>
         <v>45.400000000000006</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="12">
         <f t="shared" si="1"/>
         <v>22.700000000000003</v>
       </c>
-      <c r="L7" s="54"/>
-      <c r="M7" s="55"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="18"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="61">
+      <c r="O7" s="29"/>
+      <c r="P7" s="5">
         <f t="shared" si="2"/>
         <v>22.700000000000003</v>
       </c>
@@ -1467,35 +1452,35 @@
       <c r="B8" s="12">
         <v>590011462</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="56">
+      <c r="C8" s="49"/>
+      <c r="D8" s="12">
         <f>'Assignment 1'!AG9/10</f>
         <v>14.7</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="12">
         <f>('Quiz 1'!N9/10)*3</f>
         <v>14.700000000000001</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="12">
         <f>'Class Test 1'!O9/2</f>
         <v>19</v>
       </c>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
-      <c r="J8" s="56">
+      <c r="J8" s="12">
         <f t="shared" si="0"/>
         <v>48.4</v>
       </c>
-      <c r="K8" s="56">
+      <c r="K8" s="12">
         <f t="shared" si="1"/>
         <v>24.2</v>
       </c>
-      <c r="L8" s="54"/>
-      <c r="M8" s="55"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="18"/>
       <c r="N8" s="18"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="61">
+      <c r="O8" s="29"/>
+      <c r="P8" s="5">
         <f t="shared" si="2"/>
         <v>24.2</v>
       </c>
@@ -1514,35 +1499,35 @@
       <c r="B9" s="12">
         <v>590013559</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="56">
+      <c r="C9" s="49"/>
+      <c r="D9" s="12">
         <f>'Assignment 1'!AG10/10</f>
         <v>14.6</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="12">
         <f>('Quiz 1'!N10/10)*3</f>
         <v>6</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="12">
         <f>'Class Test 1'!O10/2</f>
         <v>15.5</v>
       </c>
       <c r="G9" s="26"/>
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
-      <c r="J9" s="56">
+      <c r="J9" s="12">
         <f t="shared" si="0"/>
         <v>36.1</v>
       </c>
-      <c r="K9" s="56">
+      <c r="K9" s="12">
         <f t="shared" si="1"/>
         <v>18.05</v>
       </c>
-      <c r="L9" s="54"/>
-      <c r="M9" s="55"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="18"/>
       <c r="N9" s="18"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="61">
+      <c r="O9" s="29"/>
+      <c r="P9" s="5">
         <f t="shared" si="2"/>
         <v>18.05</v>
       </c>
@@ -1561,35 +1546,35 @@
       <c r="B10" s="12">
         <v>590014314</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="56">
+      <c r="C10" s="49"/>
+      <c r="D10" s="12">
         <f>'Assignment 1'!AG11/10</f>
         <v>14.3</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="12">
         <f>('Quiz 1'!N11/10)*3</f>
         <v>13.200000000000001</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="12">
         <f>'Class Test 1'!O11/2</f>
         <v>19.5</v>
       </c>
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
-      <c r="J10" s="56">
+      <c r="J10" s="12">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="K10" s="56">
+      <c r="K10" s="12">
         <f t="shared" si="1"/>
         <v>23.5</v>
       </c>
-      <c r="L10" s="54"/>
-      <c r="M10" s="55"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="18"/>
       <c r="N10" s="18"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="61">
+      <c r="O10" s="29"/>
+      <c r="P10" s="5">
         <f t="shared" si="2"/>
         <v>23.5</v>
       </c>
@@ -1608,35 +1593,35 @@
       <c r="B11" s="12">
         <v>590016280</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="56">
+      <c r="C11" s="49"/>
+      <c r="D11" s="12">
         <f>'Assignment 1'!AG12/10</f>
         <v>0</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="12">
         <f>('Quiz 1'!N12/10)*3</f>
         <v>10.5</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="12">
         <f>'Class Test 1'!O12/2</f>
         <v>0</v>
       </c>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
-      <c r="J11" s="56">
+      <c r="J11" s="12">
         <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
-      <c r="K11" s="56">
+      <c r="K11" s="12">
         <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
-      <c r="L11" s="54"/>
-      <c r="M11" s="55"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="18"/>
       <c r="N11" s="18"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="61">
+      <c r="O11" s="29"/>
+      <c r="P11" s="5">
         <f t="shared" si="2"/>
         <v>5.25</v>
       </c>
@@ -1655,35 +1640,35 @@
       <c r="B12" s="12">
         <v>590017181</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="56">
+      <c r="C12" s="49"/>
+      <c r="D12" s="12">
         <f>'Assignment 1'!AG13/10</f>
         <v>14.7</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="12">
         <f>('Quiz 1'!N13/10)*3</f>
         <v>10.5</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="12">
         <f>'Class Test 1'!O13/2</f>
         <v>20</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
-      <c r="J12" s="56">
+      <c r="J12" s="12">
         <f t="shared" si="0"/>
         <v>45.2</v>
       </c>
-      <c r="K12" s="56">
+      <c r="K12" s="12">
         <f t="shared" si="1"/>
         <v>22.6</v>
       </c>
-      <c r="L12" s="54"/>
-      <c r="M12" s="55"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="18"/>
       <c r="N12" s="18"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="61">
+      <c r="O12" s="29"/>
+      <c r="P12" s="5">
         <f t="shared" si="2"/>
         <v>22.6</v>
       </c>
@@ -1702,35 +1687,35 @@
       <c r="B13" s="12">
         <v>590017658</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="56">
+      <c r="C13" s="49"/>
+      <c r="D13" s="12">
         <f>'Assignment 1'!AG14/10</f>
         <v>13.7</v>
       </c>
-      <c r="E13" s="56">
+      <c r="E13" s="12">
         <f>('Quiz 1'!N14/10)*3</f>
         <v>13.799999999999999</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="12">
         <f>'Class Test 1'!O14/2</f>
         <v>9</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
-      <c r="J13" s="56">
+      <c r="J13" s="12">
         <f t="shared" si="0"/>
         <v>36.5</v>
       </c>
-      <c r="K13" s="56">
+      <c r="K13" s="12">
         <f t="shared" si="1"/>
         <v>18.25</v>
       </c>
-      <c r="L13" s="54"/>
-      <c r="M13" s="55"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="18"/>
       <c r="N13" s="18"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="61">
+      <c r="O13" s="29"/>
+      <c r="P13" s="5">
         <f t="shared" si="2"/>
         <v>18.25</v>
       </c>
@@ -1749,35 +1734,35 @@
       <c r="B14" s="12">
         <v>590017776</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="56">
+      <c r="C14" s="49"/>
+      <c r="D14" s="12">
         <f>'Assignment 1'!AG15/10</f>
         <v>14.9</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="12">
         <f>('Quiz 1'!N15/10)*3</f>
         <v>14.700000000000001</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="12">
         <f>'Class Test 1'!O15/2</f>
         <v>17.75</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="56">
+      <c r="J14" s="12">
         <f t="shared" si="0"/>
         <v>47.35</v>
       </c>
-      <c r="K14" s="56">
+      <c r="K14" s="12">
         <f t="shared" si="1"/>
         <v>23.675000000000001</v>
       </c>
-      <c r="L14" s="54"/>
-      <c r="M14" s="55"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="18"/>
       <c r="N14" s="18"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="61">
+      <c r="O14" s="29"/>
+      <c r="P14" s="5">
         <f t="shared" si="2"/>
         <v>23.675000000000001</v>
       </c>
@@ -1796,35 +1781,35 @@
       <c r="B15" s="12">
         <v>590018198</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="56">
+      <c r="C15" s="49"/>
+      <c r="D15" s="12">
         <f>'Assignment 1'!AG16/10</f>
         <v>14.8</v>
       </c>
-      <c r="E15" s="56">
+      <c r="E15" s="12">
         <f>('Quiz 1'!N16/10)*3</f>
         <v>13.200000000000001</v>
       </c>
-      <c r="F15" s="56">
+      <c r="F15" s="12">
         <f>'Class Test 1'!O16/2</f>
         <v>20</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
-      <c r="J15" s="56">
+      <c r="J15" s="12">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="K15" s="56">
+      <c r="K15" s="12">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="L15" s="54"/>
-      <c r="M15" s="55"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="18"/>
       <c r="N15" s="18"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="61">
+      <c r="O15" s="29"/>
+      <c r="P15" s="5">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
@@ -1843,35 +1828,35 @@
       <c r="B16" s="12">
         <v>590018519</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="56">
+      <c r="C16" s="49"/>
+      <c r="D16" s="12">
         <f>'Assignment 1'!AG17/10</f>
         <v>13.9</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="12">
         <f>('Quiz 1'!N17/10)*3</f>
         <v>14.100000000000001</v>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="12">
         <f>'Class Test 1'!O17/2</f>
         <v>12</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
-      <c r="J16" s="56">
+      <c r="J16" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K16" s="56">
+      <c r="K16" s="12">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L16" s="54"/>
-      <c r="M16" s="55"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="18"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="61">
+      <c r="O16" s="29"/>
+      <c r="P16" s="5">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
@@ -1945,7 +1930,7 @@
       <c r="A20" s="30"/>
       <c r="B20" s="31"/>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20">
         <f>MAX(D5:D16)</f>
@@ -1972,7 +1957,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21">
         <f>_xlfn.MINIFS(D5:D16,D5:D16, "&gt;0")</f>
@@ -1989,7 +1974,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22">
         <f>MEDIAN(D5:D16)</f>
@@ -2184,43 +2169,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -2809,45 +2794,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:16" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -3620,81 +3605,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="45"/>
-      <c r="AD1" s="45"/>
-      <c r="AE1" s="45"/>
-      <c r="AF1" s="45"/>
-      <c r="AG1" s="45"/>
-      <c r="AH1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56"/>
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
     </row>
     <row r="2" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -3895,13 +3880,13 @@
       <c r="AH4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="50" t="s">
+      <c r="AK4" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AL4" s="50" t="s">
+      <c r="AL4" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AM4" s="51" t="s">
+      <c r="AM4" s="46" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4005,15 +3990,15 @@
         <v>150</v>
       </c>
       <c r="AH5" s="6"/>
-      <c r="AK5" s="52">
+      <c r="AK5" s="47">
         <f>SUM(C5:R5)</f>
         <v>80</v>
       </c>
-      <c r="AL5" s="52">
+      <c r="AL5" s="47">
         <f>SUM(S5:AF5)</f>
         <v>70</v>
       </c>
-      <c r="AM5" s="52">
+      <c r="AM5" s="47">
         <f>SUM(AK5:AL5)</f>
         <v>150</v>
       </c>
@@ -4122,15 +4107,15 @@
         <v>144</v>
       </c>
       <c r="AH6" s="2"/>
-      <c r="AK6" s="53">
+      <c r="AK6" s="48">
         <f t="shared" ref="AK6:AK7" si="1">SUM(C6:R6)</f>
         <v>74</v>
       </c>
-      <c r="AL6" s="53">
+      <c r="AL6" s="48">
         <f t="shared" ref="AL6:AL7" si="2">SUM(S6:AF6)</f>
         <v>70</v>
       </c>
-      <c r="AM6" s="52">
+      <c r="AM6" s="47">
         <f t="shared" ref="AM6:AM17" si="3">SUM(AK6:AL6)</f>
         <v>144</v>
       </c>
@@ -4239,15 +4224,15 @@
         <v>143</v>
       </c>
       <c r="AH7" s="2"/>
-      <c r="AK7" s="53">
+      <c r="AK7" s="48">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="AL7" s="53">
+      <c r="AL7" s="48">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="AM7" s="52">
+      <c r="AM7" s="47">
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
@@ -4356,15 +4341,15 @@
         <v>148</v>
       </c>
       <c r="AH8" s="2"/>
-      <c r="AK8" s="53">
+      <c r="AK8" s="48">
         <f t="shared" ref="AK8:AK17" si="4">SUM(C8:R8)</f>
         <v>80</v>
       </c>
-      <c r="AL8" s="53">
+      <c r="AL8" s="48">
         <f t="shared" ref="AL8:AL17" si="5">SUM(S8:AF8)</f>
         <v>68</v>
       </c>
-      <c r="AM8" s="52">
+      <c r="AM8" s="47">
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
@@ -4473,15 +4458,15 @@
         <v>147</v>
       </c>
       <c r="AH9" s="2"/>
-      <c r="AK9" s="53">
+      <c r="AK9" s="48">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL9" s="53">
+      <c r="AL9" s="48">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="AM9" s="52">
+      <c r="AM9" s="47">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
@@ -4590,15 +4575,15 @@
         <v>146</v>
       </c>
       <c r="AH10" s="2"/>
-      <c r="AK10" s="53">
+      <c r="AK10" s="48">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL10" s="53">
+      <c r="AL10" s="48">
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
-      <c r="AM10" s="52">
+      <c r="AM10" s="47">
         <f t="shared" si="3"/>
         <v>146</v>
       </c>
@@ -4707,15 +4692,15 @@
         <v>143</v>
       </c>
       <c r="AH11" s="2"/>
-      <c r="AK11" s="53">
+      <c r="AK11" s="48">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="AL11" s="53">
+      <c r="AL11" s="48">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
-      <c r="AM11" s="52">
+      <c r="AM11" s="47">
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
@@ -4764,15 +4749,15 @@
         <v>0</v>
       </c>
       <c r="AH12" s="2"/>
-      <c r="AK12" s="53">
+      <c r="AK12" s="48">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="53">
+      <c r="AL12" s="48">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="52">
+      <c r="AM12" s="47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4881,15 +4866,15 @@
         <v>147</v>
       </c>
       <c r="AH13" s="2"/>
-      <c r="AK13" s="53">
+      <c r="AK13" s="48">
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="AL13" s="53">
+      <c r="AL13" s="48">
         <f t="shared" si="5"/>
         <v>69</v>
       </c>
-      <c r="AM13" s="52">
+      <c r="AM13" s="47">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
@@ -4998,15 +4983,15 @@
         <v>137</v>
       </c>
       <c r="AH14" s="2"/>
-      <c r="AK14" s="53">
+      <c r="AK14" s="48">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="AL14" s="53">
+      <c r="AL14" s="48">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="AM14" s="52">
+      <c r="AM14" s="47">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
@@ -5115,15 +5100,15 @@
         <v>149</v>
       </c>
       <c r="AH15" s="2"/>
-      <c r="AK15" s="53">
+      <c r="AK15" s="48">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="AL15" s="53">
+      <c r="AL15" s="48">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="AM15" s="52">
+      <c r="AM15" s="47">
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
@@ -5232,15 +5217,15 @@
         <v>148</v>
       </c>
       <c r="AH16" s="2"/>
-      <c r="AK16" s="53">
+      <c r="AK16" s="48">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL16" s="53">
+      <c r="AL16" s="48">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
-      <c r="AM16" s="52">
+      <c r="AM16" s="47">
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
@@ -5349,15 +5334,15 @@
         <v>139</v>
       </c>
       <c r="AH17" s="2"/>
-      <c r="AK17" s="53">
+      <c r="AK17" s="48">
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="AL17" s="53">
+      <c r="AL17" s="48">
         <f t="shared" si="5"/>
         <v>63</v>
       </c>
-      <c r="AM17" s="52">
+      <c r="AM17" s="47">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
@@ -6150,43 +6135,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -6327,9 +6312,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2">
-        <v>10</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -6352,9 +6335,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>10</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -6377,9 +6358,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2">
-        <v>10</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -6402,9 +6381,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2">
-        <v>10</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -6427,9 +6404,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2">
-        <v>10</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -6452,9 +6427,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2">
-        <v>10</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -6477,9 +6450,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="2">
-        <v>10</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -6502,9 +6473,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="2">
-        <v>10</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -6527,9 +6496,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="2">
-        <v>10</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -6552,9 +6519,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="2">
-        <v>10</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -6577,9 +6542,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="2">
-        <v>10</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -6602,9 +6565,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="2">
-        <v>10</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -6697,43 +6658,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="A1" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -6874,9 +6835,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2">
-        <v>10</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -6899,9 +6858,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2">
-        <v>10</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -6924,9 +6881,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2">
-        <v>10</v>
-      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -6949,9 +6904,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2">
-        <v>10</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -6974,9 +6927,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2">
-        <v>10</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -6999,9 +6950,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2">
-        <v>10</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -7024,9 +6973,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="2">
-        <v>10</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -7049,9 +6996,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="2">
-        <v>10</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -7074,9 +7019,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="2">
-        <v>10</v>
-      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -7099,9 +7042,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="2">
-        <v>10</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -7124,9 +7065,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="2">
-        <v>10</v>
-      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -7149,9 +7088,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="2">
-        <v>10</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -7247,43 +7184,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -7760,43 +7697,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -8372,43 +8309,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="45" t="str">
+      <c r="A2" s="56" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="19"/>

--- a/resources/Marks/2026/even/Computational Astrophysics.xlsx
+++ b/resources/Marks/2026/even/Computational Astrophysics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Computational Astrophysics/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1905" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74388FF3-0FF2-4B9E-B496-7EB98FFD9410}"/>
+  <xr:revisionPtr revIDLastSave="1906" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13C3FF2D-4340-4BA4-A760-4205BD7E8FA4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1651,18 +1651,18 @@
       </c>
       <c r="F12" s="12">
         <f>'Class Test 1'!O13/2</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
-        <v>45.2</v>
+        <v>25.2</v>
       </c>
       <c r="K12" s="12">
         <f t="shared" si="1"/>
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="L12" s="29"/>
       <c r="M12" s="18"/>
@@ -1670,7 +1670,7 @@
       <c r="O12" s="29"/>
       <c r="P12" s="5">
         <f t="shared" si="2"/>
-        <v>22.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q12" s="35"/>
       <c r="S12" s="27" t="s">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F22">
         <f t="shared" si="6"/>
-        <v>16.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3281,41 +3281,21 @@
         <f>Marksheet!A12</f>
         <v>Shubhangee Shukla</v>
       </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2">
-        <v>3</v>
-      </c>
-      <c r="H13" s="2">
-        <v>5</v>
-      </c>
-      <c r="I13" s="2">
-        <v>5</v>
-      </c>
-      <c r="J13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2">
-        <v>5</v>
-      </c>
-      <c r="L13" s="2">
-        <v>5</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="6">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P13" s="2"/>
     </row>

--- a/resources/Marks/2026/even/Computational Astrophysics.xlsx
+++ b/resources/Marks/2026/even/Computational Astrophysics.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Computational Astrophysics/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1906" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13C3FF2D-4340-4BA4-A760-4205BD7E8FA4}"/>
+  <xr:revisionPtr revIDLastSave="2058" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FB3EC6B-031A-4AA7-AE7C-9AF0D47AD5B4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marksheet" sheetId="2" r:id="rId1"/>
     <sheet name="Quiz 1" sheetId="10" r:id="rId2"/>
     <sheet name="Class Test 1" sheetId="7" r:id="rId3"/>
     <sheet name="Assignment 1" sheetId="6" r:id="rId4"/>
-    <sheet name="Quiz 2" sheetId="11" r:id="rId5"/>
-    <sheet name="Assignment 2" sheetId="9" r:id="rId6"/>
-    <sheet name="Class Test 2" sheetId="8" r:id="rId7"/>
-    <sheet name="Mid Sem" sheetId="5" r:id="rId8"/>
+    <sheet name="Mid Sem" sheetId="5" r:id="rId5"/>
+    <sheet name="Quiz 2" sheetId="11" r:id="rId6"/>
+    <sheet name="Assignment 2" sheetId="9" r:id="rId7"/>
+    <sheet name="Class Test 2" sheetId="8" r:id="rId8"/>
     <sheet name="End Sem" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -43,30 +43,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="86">
   <si>
     <t>Final Marks</t>
   </si>
@@ -83,13 +61,22 @@
     <t>Assignment 1</t>
   </si>
   <si>
-    <t>Assignment 2</t>
+    <t>Quiz 1</t>
   </si>
   <si>
     <t>Class Test 1</t>
   </si>
   <si>
+    <t>Quiz 2</t>
+  </si>
+  <si>
+    <t>Assignment 2</t>
+  </si>
+  <si>
     <t>Class Test 2</t>
+  </si>
+  <si>
+    <t>CIA</t>
   </si>
   <si>
     <t>IA</t>
@@ -188,7 +175,13 @@
     <t>rushil.18519@stu.upes.ac.in</t>
   </si>
   <si>
-    <t>Mid Sem Examination</t>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Median</t>
   </si>
   <si>
     <t>CO1</t>
@@ -200,10 +193,13 @@
     <t>CO3</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>CO4</t>
   </si>
   <si>
-    <t>Student ID</t>
+    <t>Student Id</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
   <si>
     <t>Q1</t>
@@ -237,21 +233,6 @@
   </si>
   <si>
     <t>Q11</t>
-  </si>
-  <si>
-    <t>End Sem Examination</t>
-  </si>
-  <si>
-    <t>CO4</t>
-  </si>
-  <si>
-    <t>Student Id</t>
-  </si>
-  <si>
-    <t>Quiz 1</t>
-  </si>
-  <si>
-    <t>Quiz 2</t>
   </si>
   <si>
     <t>Q12</t>
@@ -311,112 +292,16 @@
     <t>Q30</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1: CO1 </t>
+    <t>Mid Sem Examination</t>
   </si>
   <si>
-    <t xml:space="preserve">Q2: CO1 </t>
+    <t>CO3/CO4</t>
   </si>
   <si>
-    <t xml:space="preserve">Q3: CO1 </t>
+    <t>Student ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Q4: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q5: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q6: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q7: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q8: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q9: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q10: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q11: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q12: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q13: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q14: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q15: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q16: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q17: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q18: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q19: CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q20: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q21: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q22: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q23: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q24: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q25: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q26: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q27: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q28: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q29: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q30: CO2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CO1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CO2 </t>
-  </si>
-  <si>
-    <t>CIA</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Median</t>
+    <t>End Sem Examination</t>
   </si>
 </sst>
 </file>
@@ -666,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -705,7 +590,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,6 +690,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -815,11 +705,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1140,160 +1030,160 @@
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" style="13" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="18" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" style="17" customWidth="1"/>
     <col min="13" max="16" width="13.42578125" customWidth="1"/>
     <col min="17" max="17" width="12.5703125" customWidth="1"/>
     <col min="19" max="19" width="28.7109375" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="24" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="33"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:20" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="34"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="33"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="51" t="s">
+      <c r="E3" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="K3" s="51" t="s">
+      <c r="H3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="I3" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="51" t="s">
+      <c r="J3" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="52" t="s">
+      <c r="K3" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="L3" s="50" t="s">
         <v>12</v>
       </c>
+      <c r="M3" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="50" t="s">
+        <v>15</v>
+      </c>
       <c r="S3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="28" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <f>'Assignment 1'!AG5/10</f>
         <v>15</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <f>('Quiz 1'!N5/10)*3</f>
         <v>15</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="16">
         <f>'Class Test 1'!O5/2</f>
         <v>20</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <v>15</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <v>15</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="16">
         <v>20</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="16">
         <f>SUM(D4:I4)</f>
         <v>100</v>
       </c>
-      <c r="K4" s="17">
+      <c r="K4" s="16">
         <f>J4/2</f>
         <v>50</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <f>M4/5</f>
         <v>20</v>
       </c>
-      <c r="M4" s="17">
+      <c r="M4" s="16">
         <v>100</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="16">
         <v>100</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="16">
         <f>N4*0.3</f>
         <v>30</v>
       </c>
@@ -1306,12 +1196,12 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" s="12">
         <v>590010833</v>
       </c>
-      <c r="C5" s="49"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="12">
         <f>'Assignment 1'!AG6/10</f>
         <v>14.4</v>
@@ -1324,9 +1214,9 @@
         <f>'Class Test 1'!O6/2</f>
         <v>10</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
       <c r="J5" s="12">
         <f t="shared" ref="J5:J16" si="0">SUM(D5:I5)</f>
         <v>36.4</v>
@@ -1335,77 +1225,77 @@
         <f t="shared" ref="K5:K16" si="1">J5/2</f>
         <v>18.2</v>
       </c>
-      <c r="L5" s="29"/>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="29"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="28"/>
       <c r="P5" s="5">
         <f t="shared" ref="P5:P16" si="2">SUM(K5,L5,O5)</f>
         <v>18.2</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="S5" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="T5" s="24">
+      <c r="Q5" s="34"/>
+      <c r="S5" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="T5" s="23">
         <v>182400159</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" s="12">
         <v>590010853</v>
       </c>
-      <c r="C6" s="49"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="12">
         <f>'Assignment 1'!AG7/10</f>
         <v>14.3</v>
       </c>
       <c r="E6" s="12">
         <f>('Quiz 1'!N7/10)*3</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12">
         <f>'Class Test 1'!O7/2</f>
         <v>16.5</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
       <c r="J6" s="12">
         <f t="shared" si="0"/>
-        <v>45.8</v>
+        <v>30.8</v>
       </c>
       <c r="K6" s="12">
         <f t="shared" si="1"/>
-        <v>22.9</v>
-      </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="29"/>
+        <v>15.4</v>
+      </c>
+      <c r="L6" s="28"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="28"/>
       <c r="P6" s="5">
         <f t="shared" si="2"/>
-        <v>22.9</v>
-      </c>
-      <c r="Q6" s="35"/>
-      <c r="S6" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="T6" s="24">
+        <v>15.4</v>
+      </c>
+      <c r="Q6" s="34"/>
+      <c r="S6" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" s="23">
         <v>24010310719</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" s="12">
         <v>590011314</v>
       </c>
-      <c r="C7" s="49"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="12">
         <f>'Assignment 1'!AG8/10</f>
         <v>14.8</v>
@@ -1418,9 +1308,9 @@
         <f>'Class Test 1'!O8/2</f>
         <v>16.5</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
       <c r="J7" s="12">
         <f t="shared" si="0"/>
         <v>45.400000000000006</v>
@@ -1429,30 +1319,30 @@
         <f t="shared" si="1"/>
         <v>22.700000000000003</v>
       </c>
-      <c r="L7" s="29"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="29"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="28"/>
       <c r="P7" s="5">
         <f t="shared" si="2"/>
         <v>22.700000000000003</v>
       </c>
-      <c r="Q7" s="35"/>
-      <c r="S7" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="T7" s="24">
+      <c r="Q7" s="34"/>
+      <c r="S7" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="23">
         <v>24010311286</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="12">
         <v>590011462</v>
       </c>
-      <c r="C8" s="49"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="12">
         <f>'Assignment 1'!AG9/10</f>
         <v>14.7</v>
@@ -1465,9 +1355,9 @@
         <f>'Class Test 1'!O9/2</f>
         <v>19</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
       <c r="J8" s="12">
         <f t="shared" si="0"/>
         <v>48.4</v>
@@ -1476,30 +1366,30 @@
         <f t="shared" si="1"/>
         <v>24.2</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="29"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="28"/>
       <c r="P8" s="5">
         <f t="shared" si="2"/>
         <v>24.2</v>
       </c>
-      <c r="Q8" s="35"/>
-      <c r="S8" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="24">
+      <c r="Q8" s="34"/>
+      <c r="S8" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8" s="23">
         <v>182400263</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" s="12">
         <v>590013559</v>
       </c>
-      <c r="C9" s="49"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="12">
         <f>'Assignment 1'!AG10/10</f>
         <v>14.6</v>
@@ -1512,9 +1402,9 @@
         <f>'Class Test 1'!O10/2</f>
         <v>15.5</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
       <c r="J9" s="12">
         <f t="shared" si="0"/>
         <v>36.1</v>
@@ -1523,30 +1413,30 @@
         <f t="shared" si="1"/>
         <v>18.05</v>
       </c>
-      <c r="L9" s="29"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="29"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="28"/>
       <c r="P9" s="5">
         <f t="shared" si="2"/>
         <v>18.05</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="S9" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="T9" s="24">
+      <c r="Q9" s="34"/>
+      <c r="S9" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="T9" s="23">
         <v>24010310736</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" s="12">
         <v>590014314</v>
       </c>
-      <c r="C10" s="49"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="12">
         <f>'Assignment 1'!AG11/10</f>
         <v>14.3</v>
@@ -1559,9 +1449,9 @@
         <f>'Class Test 1'!O11/2</f>
         <v>19.5</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="12">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1570,30 +1460,30 @@
         <f t="shared" si="1"/>
         <v>23.5</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="29"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="28"/>
       <c r="P10" s="5">
         <f t="shared" si="2"/>
         <v>23.5</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="S10" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="T10" s="24">
+      <c r="Q10" s="34"/>
+      <c r="S10" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="23">
         <v>24010311148</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="12">
         <v>590016280</v>
       </c>
-      <c r="C11" s="49"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="12">
         <f>'Assignment 1'!AG12/10</f>
         <v>0</v>
@@ -1606,9 +1496,9 @@
         <f>'Class Test 1'!O12/2</f>
         <v>0</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
       <c r="J11" s="12">
         <f t="shared" si="0"/>
         <v>10.5</v>
@@ -1617,30 +1507,30 @@
         <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
-      <c r="L11" s="29"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="29"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="28"/>
       <c r="P11" s="5">
         <f t="shared" si="2"/>
         <v>5.25</v>
       </c>
-      <c r="Q11" s="35"/>
-      <c r="S11" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="T11" s="24">
+      <c r="Q11" s="34"/>
+      <c r="S11" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="23">
         <v>24010310672</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B12" s="12">
         <v>590017181</v>
       </c>
-      <c r="C12" s="49"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="12">
         <f>'Assignment 1'!AG13/10</f>
         <v>14.7</v>
@@ -1653,9 +1543,9 @@
         <f>'Class Test 1'!O13/2</f>
         <v>0</v>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
       <c r="J12" s="12">
         <f t="shared" si="0"/>
         <v>25.2</v>
@@ -1664,30 +1554,30 @@
         <f t="shared" si="1"/>
         <v>12.6</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="29"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="28"/>
       <c r="P12" s="5">
         <f t="shared" si="2"/>
         <v>12.6</v>
       </c>
-      <c r="Q12" s="35"/>
-      <c r="S12" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="T12" s="24">
+      <c r="Q12" s="34"/>
+      <c r="S12" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="T12" s="23">
         <v>24010310947</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" s="12">
         <v>590017658</v>
       </c>
-      <c r="C13" s="49"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="12">
         <f>'Assignment 1'!AG14/10</f>
         <v>13.7</v>
@@ -1700,9 +1590,9 @@
         <f>'Class Test 1'!O14/2</f>
         <v>9</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
       <c r="J13" s="12">
         <f t="shared" si="0"/>
         <v>36.5</v>
@@ -1711,30 +1601,30 @@
         <f t="shared" si="1"/>
         <v>18.25</v>
       </c>
-      <c r="L13" s="29"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="29"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="28"/>
       <c r="P13" s="5">
         <f t="shared" si="2"/>
         <v>18.25</v>
       </c>
-      <c r="Q13" s="35"/>
-      <c r="S13" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="T13" s="24">
+      <c r="Q13" s="34"/>
+      <c r="S13" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="23">
         <v>182400660</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B14" s="12">
         <v>590017776</v>
       </c>
-      <c r="C14" s="49"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="12">
         <f>'Assignment 1'!AG15/10</f>
         <v>14.9</v>
@@ -1747,9 +1637,9 @@
         <f>'Class Test 1'!O15/2</f>
         <v>17.75</v>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
       <c r="J14" s="12">
         <f t="shared" si="0"/>
         <v>47.35</v>
@@ -1758,30 +1648,30 @@
         <f t="shared" si="1"/>
         <v>23.675000000000001</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="18"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="29"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="28"/>
       <c r="P14" s="5">
         <f t="shared" si="2"/>
         <v>23.675000000000001</v>
       </c>
-      <c r="Q14" s="35"/>
-      <c r="S14" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="T14" s="24">
+      <c r="Q14" s="34"/>
+      <c r="S14" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="T14" s="23">
         <v>182400665</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15" s="12">
         <v>590018198</v>
       </c>
-      <c r="C15" s="49"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="12">
         <f>'Assignment 1'!AG16/10</f>
         <v>14.8</v>
@@ -1794,9 +1684,9 @@
         <f>'Class Test 1'!O16/2</f>
         <v>20</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
       <c r="J15" s="12">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1805,30 +1695,30 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="L15" s="29"/>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="29"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="28"/>
       <c r="P15" s="5">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="Q15" s="35"/>
-      <c r="S15" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="T15" s="24">
+      <c r="Q15" s="34"/>
+      <c r="S15" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="T15" s="23">
         <v>182400712</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B16" s="12">
         <v>590018519</v>
       </c>
-      <c r="C16" s="49"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="12">
         <f>'Assignment 1'!AG17/10</f>
         <v>13.9</v>
@@ -1841,9 +1731,9 @@
         <f>'Class Test 1'!O17/2</f>
         <v>12</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
       <c r="J16" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1852,85 +1742,85 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="29"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="28"/>
       <c r="P16" s="5">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="Q16" s="35"/>
-      <c r="S16" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="T16" s="24">
+      <c r="Q16" s="34"/>
+      <c r="S16" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="T16" s="23">
         <v>24010311320</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="44"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
       <c r="U17" t="str">
         <f t="shared" ref="U17" si="3">LOWER(S17)</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="29"/>
+      <c r="A18" s="29"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="28"/>
       <c r="P18" s="7"/>
     </row>
     <row r="19" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="29"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="28"/>
       <c r="P19" s="7"/>
     </row>
     <row r="20" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="30"/>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="D20">
         <f>MAX(D5:D16)</f>
@@ -1938,26 +1828,26 @@
       </c>
       <c r="E20">
         <f t="shared" ref="E20:F20" si="4">MAX(E5:E16)</f>
-        <v>15</v>
+        <v>14.700000000000001</v>
       </c>
       <c r="F20">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="29"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="28"/>
       <c r="P20" s="7"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="D21">
         <f>_xlfn.MINIFS(D5:D16,D5:D16, "&gt;0")</f>
@@ -1974,7 +1864,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <f>MEDIAN(D5:D16)</f>
@@ -1982,7 +1872,7 @@
       </c>
       <c r="E22">
         <f t="shared" ref="E22:F22" si="6">MEDIAN(E5:E16)</f>
-        <v>13.5</v>
+        <v>13.200000000000001</v>
       </c>
       <c r="F22">
         <f t="shared" si="6"/>
@@ -1992,147 +1882,147 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="H23" s="13"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="17"/>
       <c r="L23"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24" s="13"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
       <c r="J24"/>
       <c r="L24"/>
-      <c r="Q24" s="24"/>
+      <c r="Q24" s="23"/>
       <c r="T24"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B25"/>
       <c r="C25" s="13"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="Q25" s="24"/>
+      <c r="Q25" s="23"/>
       <c r="T25"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B26"/>
       <c r="C26" s="13"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
       <c r="J26"/>
       <c r="L26"/>
-      <c r="Q26" s="24"/>
+      <c r="Q26" s="23"/>
       <c r="T26"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B27"/>
       <c r="C27" s="13"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
       <c r="J27"/>
       <c r="L27"/>
-      <c r="Q27" s="24"/>
+      <c r="Q27" s="23"/>
       <c r="T27"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B28"/>
       <c r="C28" s="13"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
       <c r="J28"/>
       <c r="L28"/>
-      <c r="Q28" s="24"/>
+      <c r="Q28" s="23"/>
       <c r="T28"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B29"/>
       <c r="C29" s="13"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
       <c r="J29"/>
       <c r="L29"/>
-      <c r="Q29" s="24"/>
+      <c r="Q29" s="23"/>
       <c r="T29"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B30"/>
       <c r="C30" s="13"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
       <c r="J30"/>
       <c r="L30"/>
-      <c r="Q30" s="24"/>
+      <c r="Q30" s="23"/>
       <c r="T30"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B31"/>
       <c r="C31" s="13"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
       <c r="J31"/>
       <c r="L31"/>
-      <c r="Q31" s="24"/>
+      <c r="Q31" s="23"/>
       <c r="T31"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B32"/>
       <c r="C32" s="13"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
       <c r="J32"/>
       <c r="L32"/>
-      <c r="Q32" s="24"/>
+      <c r="Q32" s="23"/>
       <c r="T32"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33"/>
       <c r="C33" s="13"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
       <c r="J33"/>
       <c r="L33"/>
-      <c r="Q33" s="24"/>
+      <c r="Q33" s="23"/>
       <c r="T33"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34"/>
       <c r="C34" s="13"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
       <c r="J34"/>
       <c r="L34"/>
-      <c r="Q34" s="24"/>
+      <c r="Q34" s="23"/>
       <c r="T34"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35"/>
       <c r="C35" s="13"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
       <c r="J35"/>
       <c r="L35"/>
-      <c r="Q35" s="24"/>
+      <c r="Q35" s="23"/>
       <c r="T35"/>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36"/>
       <c r="C36" s="13"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
       <c r="J36"/>
       <c r="L36"/>
-      <c r="Q36" s="24"/>
+      <c r="Q36" s="23"/>
       <c r="T36"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37"/>
       <c r="C37" s="13"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
       <c r="J37"/>
       <c r="L37"/>
-      <c r="Q37" s="24"/>
+      <c r="Q37" s="23"/>
       <c r="T37"/>
     </row>
   </sheetData>
@@ -2158,7 +2048,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F273A3AF-2289-4EB8-9907-58DA32095A7D}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -2168,59 +2058,59 @@
     <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-    </row>
-    <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+    <row r="1" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+    </row>
+    <row r="2" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -2232,24 +2122,24 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -2259,16 +2149,31 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>10</v>
@@ -2294,8 +2199,28 @@
         <v>50</v>
       </c>
       <c r="O5" s="6"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S5" s="6">
+        <f>C5</f>
+        <v>10</v>
+      </c>
+      <c r="T5" s="6">
+        <f>D5</f>
+        <v>10</v>
+      </c>
+      <c r="U5" s="6">
+        <f>E5</f>
+        <v>15</v>
+      </c>
+      <c r="V5" s="6">
+        <f>F5</f>
+        <v>15</v>
+      </c>
+      <c r="W5">
+        <f>SUM(S5:V5)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>'Mid Sem'!B6</f>
         <v>590010833</v>
@@ -2328,8 +2253,28 @@
         <v>40</v>
       </c>
       <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S6" s="6">
+        <f t="shared" ref="S6:S18" si="1">C6</f>
+        <v>10</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" ref="T6:T18" si="2">D6</f>
+        <v>10</v>
+      </c>
+      <c r="U6" s="6">
+        <f t="shared" ref="U6:U18" si="3">E6</f>
+        <v>6</v>
+      </c>
+      <c r="V6" s="6">
+        <f t="shared" ref="V6:V18" si="4">F6</f>
+        <v>14</v>
+      </c>
+      <c r="W6">
+        <f t="shared" ref="W6:W18" si="5">SUM(S6:V6)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>'Mid Sem'!B7</f>
         <v>590010853</v>
@@ -2338,18 +2283,10 @@
         <f>'Mid Sem'!A7</f>
         <v>Mokshika Saini</v>
       </c>
-      <c r="C7" s="2">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2">
-        <v>15</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -2359,11 +2296,31 @@
       <c r="M7" s="2"/>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V7" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>'Mid Sem'!B8</f>
         <v>590011314</v>
@@ -2396,8 +2353,28 @@
         <v>47</v>
       </c>
       <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S8" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U8" s="6">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V8" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>'Mid Sem'!B9</f>
         <v>590011462</v>
@@ -2430,8 +2407,28 @@
         <v>49</v>
       </c>
       <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S9" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T9" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="V9" s="6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>'Mid Sem'!B10</f>
         <v>590013559</v>
@@ -2464,8 +2461,28 @@
         <v>20</v>
       </c>
       <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S10" s="6">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T10" s="6">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="U10" s="6">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="V10" s="6">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>'Mid Sem'!B11</f>
         <v>590014314</v>
@@ -2498,8 +2515,28 @@
         <v>44</v>
       </c>
       <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S11" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T11" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U11" s="6">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="V11" s="6">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f>'Mid Sem'!B12</f>
         <v>590016280</v>
@@ -2532,8 +2569,28 @@
         <v>35</v>
       </c>
       <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S12" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>'Mid Sem'!B13</f>
         <v>590017181</v>
@@ -2566,8 +2623,28 @@
         <v>35</v>
       </c>
       <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S13" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T13" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U13" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="5"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f>'Mid Sem'!B14</f>
         <v>590017658</v>
@@ -2600,8 +2677,28 @@
         <v>46</v>
       </c>
       <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S14" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T14" s="6">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="U14" s="6">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="V14" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="5"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f>'Mid Sem'!B15</f>
         <v>590017776</v>
@@ -2634,8 +2731,28 @@
         <v>49</v>
       </c>
       <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S15" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T15" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U15" s="6">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="V15" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f>'Mid Sem'!B16</f>
         <v>590018198</v>
@@ -2668,8 +2785,28 @@
         <v>44</v>
       </c>
       <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S16" s="6">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="T16" s="6">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="U16" s="6">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="V16" s="6">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="5"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>'Mid Sem'!B17</f>
         <v>590018519</v>
@@ -2702,8 +2839,28 @@
         <v>47</v>
       </c>
       <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S17" s="6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="T17" s="6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U17" s="6">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="V17" s="6">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2"/>
@@ -2719,8 +2876,28 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="2"/>
@@ -2737,7 +2914,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="2"/>
@@ -2754,7 +2931,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="2"/>
@@ -2782,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC20399B-538A-4326-81D5-F56BB2966D2A}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -2793,137 +2970,152 @@
     <col min="16" max="16" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-    </row>
-    <row r="2" spans="1:16" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+    </row>
+    <row r="2" spans="1:23" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>3</v>
@@ -2962,8 +3154,22 @@
         <v>40</v>
       </c>
       <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S5" s="12">
+        <f>SUM(D5,C5,I5,L5)</f>
+        <v>16</v>
+      </c>
+      <c r="T5" s="12">
+        <f>SUM(G5,F5,E5,H5,J5,K5)</f>
+        <v>24</v>
+      </c>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5">
+        <f>SUM(S5:V5)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>Marksheet!B5</f>
         <v>590010833</v>
@@ -3009,8 +3215,22 @@
         <v>20</v>
       </c>
       <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S6" s="12">
+        <f t="shared" ref="S6:S17" si="1">SUM(D6,C6,I6,L6)</f>
+        <v>6</v>
+      </c>
+      <c r="T6" s="12">
+        <f t="shared" ref="T6:T17" si="2">SUM(G6,F6,E6,H6,J6,K6)</f>
+        <v>14</v>
+      </c>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6">
+        <f t="shared" ref="W6:W17" si="3">SUM(S6:V6)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>Marksheet!B6</f>
         <v>590010853</v>
@@ -3056,8 +3276,22 @@
         <v>33</v>
       </c>
       <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S7" s="12">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="T7" s="12">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>Marksheet!B7</f>
         <v>590011314</v>
@@ -3103,8 +3337,22 @@
         <v>33</v>
       </c>
       <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S8" s="12">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T8" s="12">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>Marksheet!B8</f>
         <v>590011462</v>
@@ -3150,8 +3398,22 @@
         <v>38</v>
       </c>
       <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S9" s="12">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="T9" s="12">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>Marksheet!B9</f>
         <v>590013559</v>
@@ -3197,8 +3459,22 @@
         <v>31</v>
       </c>
       <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S10" s="12">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T10" s="12">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>Marksheet!B10</f>
         <v>590014314</v>
@@ -3244,8 +3520,22 @@
         <v>39</v>
       </c>
       <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S11" s="12">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T11" s="12">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <f>Marksheet!B11</f>
         <v>590016280</v>
@@ -3271,8 +3561,22 @@
         <v>0</v>
       </c>
       <c r="P12" s="2"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S12" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <f>Marksheet!B12</f>
         <v>590017181</v>
@@ -3298,8 +3602,22 @@
         <v>0</v>
       </c>
       <c r="P13" s="2"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S13" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <f>Marksheet!B13</f>
         <v>590017658</v>
@@ -3345,8 +3663,22 @@
         <v>18</v>
       </c>
       <c r="P14" s="2"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S14" s="12">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T14" s="12">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <f>Marksheet!B14</f>
         <v>590017776</v>
@@ -3392,8 +3724,22 @@
         <v>35.5</v>
       </c>
       <c r="P15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S15" s="12">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="T15" s="12">
+        <f t="shared" si="2"/>
+        <v>21.5</v>
+      </c>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15">
+        <f t="shared" si="3"/>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <f>Marksheet!B15</f>
         <v>590018198</v>
@@ -3439,8 +3785,22 @@
         <v>40</v>
       </c>
       <c r="P16" s="2"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S16" s="12">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="T16" s="12">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>Marksheet!B16</f>
         <v>590018519</v>
@@ -3486,8 +3846,22 @@
         <v>24</v>
       </c>
       <c r="P17" s="2"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="S17" s="12">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="T17" s="12">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2"/>
@@ -3505,7 +3879,7 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="2"/>
@@ -3523,7 +3897,7 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -3541,7 +3915,7 @@
       <c r="O20" s="2"/>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -3571,7 +3945,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA02827-4102-4501-99F8-C9B7DD668F03}">
-  <dimension ref="A1:AM82"/>
+  <dimension ref="A1:AM21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -3585,295 +3959,295 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56"/>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="52"/>
+      <c r="AC1" s="52"/>
+      <c r="AD1" s="52"/>
+      <c r="AE1" s="52"/>
+      <c r="AF1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
     </row>
     <row r="2" spans="1:39" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="57"/>
-      <c r="Z2" s="57"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="57"/>
-      <c r="AC2" s="57"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="57"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="AL4" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="AH4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK4" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="AL4" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM4" s="46" t="s">
-        <v>11</v>
+      <c r="AM4" s="45" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>5</v>
@@ -3970,15 +4344,15 @@
         <v>150</v>
       </c>
       <c r="AH5" s="6"/>
-      <c r="AK5" s="47">
+      <c r="AK5" s="46">
         <f>SUM(C5:R5)</f>
         <v>80</v>
       </c>
-      <c r="AL5" s="47">
+      <c r="AL5" s="46">
         <f>SUM(S5:AF5)</f>
         <v>70</v>
       </c>
-      <c r="AM5" s="47">
+      <c r="AM5" s="46">
         <f>SUM(AK5:AL5)</f>
         <v>150</v>
       </c>
@@ -4087,15 +4461,15 @@
         <v>144</v>
       </c>
       <c r="AH6" s="2"/>
-      <c r="AK6" s="48">
+      <c r="AK6" s="47">
         <f t="shared" ref="AK6:AK7" si="1">SUM(C6:R6)</f>
         <v>74</v>
       </c>
-      <c r="AL6" s="48">
+      <c r="AL6" s="47">
         <f t="shared" ref="AL6:AL7" si="2">SUM(S6:AF6)</f>
         <v>70</v>
       </c>
-      <c r="AM6" s="47">
+      <c r="AM6" s="46">
         <f t="shared" ref="AM6:AM17" si="3">SUM(AK6:AL6)</f>
         <v>144</v>
       </c>
@@ -4204,15 +4578,15 @@
         <v>143</v>
       </c>
       <c r="AH7" s="2"/>
-      <c r="AK7" s="48">
+      <c r="AK7" s="47">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="AL7" s="48">
+      <c r="AL7" s="47">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="AM7" s="47">
+      <c r="AM7" s="46">
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
@@ -4321,15 +4695,15 @@
         <v>148</v>
       </c>
       <c r="AH8" s="2"/>
-      <c r="AK8" s="48">
+      <c r="AK8" s="47">
         <f t="shared" ref="AK8:AK17" si="4">SUM(C8:R8)</f>
         <v>80</v>
       </c>
-      <c r="AL8" s="48">
+      <c r="AL8" s="47">
         <f t="shared" ref="AL8:AL17" si="5">SUM(S8:AF8)</f>
         <v>68</v>
       </c>
-      <c r="AM8" s="47">
+      <c r="AM8" s="46">
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
@@ -4438,15 +4812,15 @@
         <v>147</v>
       </c>
       <c r="AH9" s="2"/>
-      <c r="AK9" s="48">
+      <c r="AK9" s="47">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL9" s="48">
+      <c r="AL9" s="47">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="AM9" s="47">
+      <c r="AM9" s="46">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
@@ -4555,15 +4929,15 @@
         <v>146</v>
       </c>
       <c r="AH10" s="2"/>
-      <c r="AK10" s="48">
+      <c r="AK10" s="47">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL10" s="48">
+      <c r="AL10" s="47">
         <f t="shared" si="5"/>
         <v>66</v>
       </c>
-      <c r="AM10" s="47">
+      <c r="AM10" s="46">
         <f t="shared" si="3"/>
         <v>146</v>
       </c>
@@ -4672,15 +5046,15 @@
         <v>143</v>
       </c>
       <c r="AH11" s="2"/>
-      <c r="AK11" s="48">
+      <c r="AK11" s="47">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="AL11" s="48">
+      <c r="AL11" s="47">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
-      <c r="AM11" s="47">
+      <c r="AM11" s="46">
         <f t="shared" si="3"/>
         <v>143</v>
       </c>
@@ -4729,15 +5103,15 @@
         <v>0</v>
       </c>
       <c r="AH12" s="2"/>
-      <c r="AK12" s="48">
+      <c r="AK12" s="47">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL12" s="48">
+      <c r="AL12" s="47">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AM12" s="47">
+      <c r="AM12" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4846,15 +5220,15 @@
         <v>147</v>
       </c>
       <c r="AH13" s="2"/>
-      <c r="AK13" s="48">
+      <c r="AK13" s="47">
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="AL13" s="48">
+      <c r="AL13" s="47">
         <f t="shared" si="5"/>
         <v>69</v>
       </c>
-      <c r="AM13" s="47">
+      <c r="AM13" s="46">
         <f t="shared" si="3"/>
         <v>147</v>
       </c>
@@ -4963,15 +5337,15 @@
         <v>137</v>
       </c>
       <c r="AH14" s="2"/>
-      <c r="AK14" s="48">
+      <c r="AK14" s="47">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="AL14" s="48">
+      <c r="AL14" s="47">
         <f t="shared" si="5"/>
         <v>67</v>
       </c>
-      <c r="AM14" s="47">
+      <c r="AM14" s="46">
         <f t="shared" si="3"/>
         <v>137</v>
       </c>
@@ -5080,15 +5454,15 @@
         <v>149</v>
       </c>
       <c r="AH15" s="2"/>
-      <c r="AK15" s="48">
+      <c r="AK15" s="47">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="AL15" s="48">
+      <c r="AL15" s="47">
         <f t="shared" si="5"/>
         <v>70</v>
       </c>
-      <c r="AM15" s="47">
+      <c r="AM15" s="46">
         <f t="shared" si="3"/>
         <v>149</v>
       </c>
@@ -5197,15 +5571,15 @@
         <v>148</v>
       </c>
       <c r="AH16" s="2"/>
-      <c r="AK16" s="48">
+      <c r="AK16" s="47">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="AL16" s="48">
+      <c r="AL16" s="47">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
-      <c r="AM16" s="47">
+      <c r="AM16" s="46">
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
@@ -5314,15 +5688,15 @@
         <v>139</v>
       </c>
       <c r="AH17" s="2"/>
-      <c r="AK17" s="48">
+      <c r="AK17" s="47">
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="AL17" s="48">
+      <c r="AL17" s="47">
         <f t="shared" si="5"/>
         <v>63</v>
       </c>
-      <c r="AM17" s="47">
+      <c r="AM17" s="46">
         <f t="shared" si="3"/>
         <v>139</v>
       </c>
@@ -5474,624 +5848,6 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="str" cm="1">
-        <f t="array" ref="F25:G25">_xlfn.TEXTSPLIT(E25, ":")</f>
-        <v>Q1</v>
-      </c>
-      <c r="G25" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" t="str" cm="1">
-        <f t="array" ref="F26:G26">_xlfn.TEXTSPLIT(E26, ":")</f>
-        <v>Q2</v>
-      </c>
-      <c r="G26" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="F27" t="e" cm="1">
-        <f t="array" ref="F27">_xlfn.TEXTSPLIT(E27, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="E28" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28" t="str" cm="1">
-        <f t="array" ref="F28:G28">_xlfn.TEXTSPLIT(E28, ":")</f>
-        <v>Q3</v>
-      </c>
-      <c r="G28" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="F29" t="e" cm="1">
-        <f t="array" ref="F29">_xlfn.TEXTSPLIT(E29, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="E30" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" t="str" cm="1">
-        <f t="array" ref="F30:G30">_xlfn.TEXTSPLIT(E30, ":")</f>
-        <v>Q4</v>
-      </c>
-      <c r="G30" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="F31" t="e" cm="1">
-        <f t="array" ref="F31">_xlfn.TEXTSPLIT(E31, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="J31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="E32" t="s">
-        <v>85</v>
-      </c>
-      <c r="F32" t="str" cm="1">
-        <f t="array" ref="F32:G32">_xlfn.TEXTSPLIT(E32, ":")</f>
-        <v>Q5</v>
-      </c>
-      <c r="G32" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F33" t="e" cm="1">
-        <f t="array" ref="F33">_xlfn.TEXTSPLIT(E33, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E34" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" t="str" cm="1">
-        <f t="array" ref="F34:G34">_xlfn.TEXTSPLIT(E34, ":")</f>
-        <v>Q6</v>
-      </c>
-      <c r="G34" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F35" t="e" cm="1">
-        <f t="array" ref="F35">_xlfn.TEXTSPLIT(E35, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E36" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" t="str" cm="1">
-        <f t="array" ref="F36:G36">_xlfn.TEXTSPLIT(E36, ":")</f>
-        <v>Q7</v>
-      </c>
-      <c r="G36" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F37" t="e" cm="1">
-        <f t="array" ref="F37">_xlfn.TEXTSPLIT(E37, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="38" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" t="str" cm="1">
-        <f t="array" ref="F38:G38">_xlfn.TEXTSPLIT(E38, ":")</f>
-        <v>Q8</v>
-      </c>
-      <c r="G38" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F39" t="e" cm="1">
-        <f t="array" ref="F39">_xlfn.TEXTSPLIT(E39, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" t="str" cm="1">
-        <f t="array" ref="F40:G40">_xlfn.TEXTSPLIT(E40, ":")</f>
-        <v>Q9</v>
-      </c>
-      <c r="G40" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F41" t="e" cm="1">
-        <f t="array" ref="F41">_xlfn.TEXTSPLIT(E41, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="42" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
-        <v>90</v>
-      </c>
-      <c r="F42" t="str" cm="1">
-        <f t="array" ref="F42:G42">_xlfn.TEXTSPLIT(E42, ":")</f>
-        <v>Q10</v>
-      </c>
-      <c r="G42" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J42" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F43" t="e" cm="1">
-        <f t="array" ref="F43">_xlfn.TEXTSPLIT(E43, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" t="str" cm="1">
-        <f t="array" ref="F44:G44">_xlfn.TEXTSPLIT(E44, ":")</f>
-        <v>Q11</v>
-      </c>
-      <c r="G44" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F45" t="e" cm="1">
-        <f t="array" ref="F45">_xlfn.TEXTSPLIT(E45, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="46" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E46" t="s">
-        <v>92</v>
-      </c>
-      <c r="F46" t="str" cm="1">
-        <f t="array" ref="F46:G46">_xlfn.TEXTSPLIT(E46, ":")</f>
-        <v>Q12</v>
-      </c>
-      <c r="G46" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F47" t="e" cm="1">
-        <f t="array" ref="F47">_xlfn.TEXTSPLIT(E47, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="48" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E48" t="s">
-        <v>93</v>
-      </c>
-      <c r="F48" t="str" cm="1">
-        <f t="array" ref="F48:G48">_xlfn.TEXTSPLIT(E48, ":")</f>
-        <v>Q13</v>
-      </c>
-      <c r="G48" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F49" t="e" cm="1">
-        <f t="array" ref="F49">_xlfn.TEXTSPLIT(E49, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E50" t="s">
-        <v>94</v>
-      </c>
-      <c r="F50" t="str" cm="1">
-        <f t="array" ref="F50:G50">_xlfn.TEXTSPLIT(E50, ":")</f>
-        <v>Q14</v>
-      </c>
-      <c r="G50" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F51" t="e" cm="1">
-        <f t="array" ref="F51">_xlfn.TEXTSPLIT(E51, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E52" t="s">
-        <v>95</v>
-      </c>
-      <c r="F52" t="str" cm="1">
-        <f t="array" ref="F52:G52">_xlfn.TEXTSPLIT(E52, ":")</f>
-        <v>Q15</v>
-      </c>
-      <c r="G52" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J52" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F53" t="e" cm="1">
-        <f t="array" ref="F53">_xlfn.TEXTSPLIT(E53, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="54" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E54" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" t="str" cm="1">
-        <f t="array" ref="F54:G54">_xlfn.TEXTSPLIT(E54, ":")</f>
-        <v>Q16</v>
-      </c>
-      <c r="G54" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J54" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F55" t="e" cm="1">
-        <f t="array" ref="F55">_xlfn.TEXTSPLIT(E55, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="56" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E56" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" t="str" cm="1">
-        <f t="array" ref="F56:G56">_xlfn.TEXTSPLIT(E56, ":")</f>
-        <v>Q17</v>
-      </c>
-      <c r="G56" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J56" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F57" t="e" cm="1">
-        <f t="array" ref="F57">_xlfn.TEXTSPLIT(E57, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="58" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E58" t="s">
-        <v>98</v>
-      </c>
-      <c r="F58" t="str" cm="1">
-        <f t="array" ref="F58:G58">_xlfn.TEXTSPLIT(E58, ":")</f>
-        <v>Q18</v>
-      </c>
-      <c r="G58" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J58" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F59" t="e" cm="1">
-        <f t="array" ref="F59">_xlfn.TEXTSPLIT(E59, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="60" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E60" t="s">
-        <v>99</v>
-      </c>
-      <c r="F60" t="str" cm="1">
-        <f t="array" ref="F60:G60">_xlfn.TEXTSPLIT(E60, ":")</f>
-        <v>Q19</v>
-      </c>
-      <c r="G60" t="str">
-        <v xml:space="preserve"> CO1 </v>
-      </c>
-      <c r="J60" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F61" t="e" cm="1">
-        <f t="array" ref="F61">_xlfn.TEXTSPLIT(E61, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="62" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E62" t="s">
-        <v>100</v>
-      </c>
-      <c r="F62" t="str" cm="1">
-        <f t="array" ref="F62:G62">_xlfn.TEXTSPLIT(E62, ":")</f>
-        <v>Q20</v>
-      </c>
-      <c r="G62" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J62" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="63" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F63" t="e" cm="1">
-        <f t="array" ref="F63">_xlfn.TEXTSPLIT(E63, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="64" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E64" t="s">
-        <v>101</v>
-      </c>
-      <c r="F64" t="str" cm="1">
-        <f t="array" ref="F64:G64">_xlfn.TEXTSPLIT(E64, ":")</f>
-        <v>Q21</v>
-      </c>
-      <c r="G64" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F65" t="e" cm="1">
-        <f t="array" ref="F65">_xlfn.TEXTSPLIT(E65, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="66" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E66" t="s">
-        <v>102</v>
-      </c>
-      <c r="F66" t="str" cm="1">
-        <f t="array" ref="F66:G66">_xlfn.TEXTSPLIT(E66, ":")</f>
-        <v>Q22</v>
-      </c>
-      <c r="G66" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J66" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="67" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F67" t="e" cm="1">
-        <f t="array" ref="F67">_xlfn.TEXTSPLIT(E67, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="68" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E68" t="s">
-        <v>103</v>
-      </c>
-      <c r="F68" t="str" cm="1">
-        <f t="array" ref="F68:G68">_xlfn.TEXTSPLIT(E68, ":")</f>
-        <v>Q23</v>
-      </c>
-      <c r="G68" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J68" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="69" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F69" t="e" cm="1">
-        <f t="array" ref="F69">_xlfn.TEXTSPLIT(E69, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="70" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E70" t="s">
-        <v>104</v>
-      </c>
-      <c r="F70" t="str" cm="1">
-        <f t="array" ref="F70:G70">_xlfn.TEXTSPLIT(E70, ":")</f>
-        <v>Q24</v>
-      </c>
-      <c r="G70" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J70" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F71" t="e" cm="1">
-        <f t="array" ref="F71">_xlfn.TEXTSPLIT(E71, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="72" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E72" t="s">
-        <v>105</v>
-      </c>
-      <c r="F72" t="str" cm="1">
-        <f t="array" ref="F72:G72">_xlfn.TEXTSPLIT(E72, ":")</f>
-        <v>Q25</v>
-      </c>
-      <c r="G72" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J72" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="73" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F73" t="e" cm="1">
-        <f t="array" ref="F73">_xlfn.TEXTSPLIT(E73, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="74" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E74" t="s">
-        <v>106</v>
-      </c>
-      <c r="F74" t="str" cm="1">
-        <f t="array" ref="F74:G74">_xlfn.TEXTSPLIT(E74, ":")</f>
-        <v>Q26</v>
-      </c>
-      <c r="G74" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J74" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F75" t="e" cm="1">
-        <f t="array" ref="F75">_xlfn.TEXTSPLIT(E75, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="76" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E76" t="s">
-        <v>107</v>
-      </c>
-      <c r="F76" t="str" cm="1">
-        <f t="array" ref="F76:G76">_xlfn.TEXTSPLIT(E76, ":")</f>
-        <v>Q27</v>
-      </c>
-      <c r="G76" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-      <c r="J76" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="77" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F77" t="e" cm="1">
-        <f t="array" ref="F77">_xlfn.TEXTSPLIT(E77, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="78" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E78" t="s">
-        <v>108</v>
-      </c>
-      <c r="F78" t="str" cm="1">
-        <f t="array" ref="F78:G78">_xlfn.TEXTSPLIT(E78, ":")</f>
-        <v>Q28</v>
-      </c>
-      <c r="G78" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-    </row>
-    <row r="79" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="F79" t="e" cm="1">
-        <f t="array" ref="F79">_xlfn.TEXTSPLIT(E79, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="80" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E80" t="s">
-        <v>109</v>
-      </c>
-      <c r="F80" t="str" cm="1">
-        <f t="array" ref="F80:G80">_xlfn.TEXTSPLIT(E80, ":")</f>
-        <v>Q29</v>
-      </c>
-      <c r="G80" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-    </row>
-    <row r="81" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="F81" t="e" cm="1">
-        <f t="array" ref="F81">_xlfn.TEXTSPLIT(E81, ":")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="82" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E82" t="s">
-        <v>110</v>
-      </c>
-      <c r="F82" t="str" cm="1">
-        <f t="array" ref="F82:G82">_xlfn.TEXTSPLIT(E82, ":")</f>
-        <v>Q30</v>
-      </c>
-      <c r="G82" t="str">
-        <v xml:space="preserve"> CO2 </v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:AH1"/>
@@ -6103,6 +5859,1177 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355320EC-5887-4CA4-8B00-C82693C60F77}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" style="13" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A1" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+    </row>
+    <row r="2" spans="1:22" ht="24.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="52" t="str">
+        <f>Marksheet!A2</f>
+        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="9">
+        <v>6</v>
+      </c>
+      <c r="D5" s="9">
+        <v>6</v>
+      </c>
+      <c r="E5" s="9">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9">
+        <v>6</v>
+      </c>
+      <c r="G5" s="9">
+        <v>6</v>
+      </c>
+      <c r="H5" s="9">
+        <v>15</v>
+      </c>
+      <c r="I5" s="9">
+        <v>15</v>
+      </c>
+      <c r="J5" s="9">
+        <v>15</v>
+      </c>
+      <c r="K5" s="9">
+        <v>25</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9">
+        <f>SUM(C5:K5)</f>
+        <v>100</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="R5" s="12">
+        <f>SUM(C5,E5)</f>
+        <v>12</v>
+      </c>
+      <c r="S5" s="12">
+        <f>SUM(D5,F5,H5,J5)</f>
+        <v>42</v>
+      </c>
+      <c r="T5" s="5">
+        <f>SUM(K5)*3/5</f>
+        <v>15</v>
+      </c>
+      <c r="U5" s="5">
+        <f>G5 + I5 + K5*2/5</f>
+        <v>31</v>
+      </c>
+      <c r="V5">
+        <f>SUM(R5:U5)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="str">
+        <f>Marksheet!A5</f>
+        <v>Vansh Sharma</v>
+      </c>
+      <c r="B6" s="14">
+        <f>Marksheet!B5</f>
+        <v>590010833</v>
+      </c>
+      <c r="C6" s="57">
+        <v>4</v>
+      </c>
+      <c r="D6" s="57">
+        <v>3</v>
+      </c>
+      <c r="E6" s="57">
+        <v>6</v>
+      </c>
+      <c r="F6" s="57">
+        <v>2</v>
+      </c>
+      <c r="G6" s="57">
+        <v>2</v>
+      </c>
+      <c r="H6" s="57">
+        <v>4</v>
+      </c>
+      <c r="I6" s="57">
+        <v>4</v>
+      </c>
+      <c r="J6" s="57">
+        <v>7</v>
+      </c>
+      <c r="K6" s="57">
+        <v>10</v>
+      </c>
+      <c r="L6" s="57"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="9">
+        <f>SUM(C6:K6)</f>
+        <v>42</v>
+      </c>
+      <c r="O6" s="2"/>
+      <c r="R6" s="12">
+        <f t="shared" ref="R6:R21" si="0">SUM(C6,E6)</f>
+        <v>10</v>
+      </c>
+      <c r="S6" s="12">
+        <f t="shared" ref="S6:S21" si="1">SUM(D6,F6,H6,J6)</f>
+        <v>16</v>
+      </c>
+      <c r="T6" s="5">
+        <f t="shared" ref="T6:T21" si="2">SUM(K6)*3/5</f>
+        <v>6</v>
+      </c>
+      <c r="U6" s="5">
+        <f t="shared" ref="U6:U21" si="3">G6 + I6 + K6*2/5</f>
+        <v>10</v>
+      </c>
+      <c r="V6">
+        <f t="shared" ref="V6:V21" si="4">SUM(R6:U6)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="str">
+        <f>Marksheet!A6</f>
+        <v>Mokshika Saini</v>
+      </c>
+      <c r="B7" s="14">
+        <f>Marksheet!B6</f>
+        <v>590010853</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="9">
+        <f t="shared" ref="N7:N21" si="5">SUM(C7:H7)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="2"/>
+      <c r="R7" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="str">
+        <f>Marksheet!A7</f>
+        <v>Sakshi Sheshrao Charde</v>
+      </c>
+      <c r="B8" s="14">
+        <f>Marksheet!B7</f>
+        <v>590011314</v>
+      </c>
+      <c r="C8" s="57">
+        <v>4</v>
+      </c>
+      <c r="D8" s="57">
+        <v>4</v>
+      </c>
+      <c r="E8" s="57">
+        <v>6</v>
+      </c>
+      <c r="F8" s="57">
+        <v>4</v>
+      </c>
+      <c r="G8" s="57">
+        <v>6</v>
+      </c>
+      <c r="H8" s="57">
+        <v>9</v>
+      </c>
+      <c r="I8" s="57">
+        <v>2</v>
+      </c>
+      <c r="J8" s="57">
+        <v>5</v>
+      </c>
+      <c r="K8" s="57">
+        <v>0</v>
+      </c>
+      <c r="L8" s="57"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="9">
+        <f>SUM(C8:K8)</f>
+        <v>40</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="R8" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="S8" s="12">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="str">
+        <f>Marksheet!A8</f>
+        <v>Akash Vinodshirke</v>
+      </c>
+      <c r="B9" s="14">
+        <f>Marksheet!B8</f>
+        <v>590011462</v>
+      </c>
+      <c r="C9" s="57">
+        <v>6</v>
+      </c>
+      <c r="D9" s="57">
+        <v>6</v>
+      </c>
+      <c r="E9" s="57">
+        <v>6</v>
+      </c>
+      <c r="F9" s="57">
+        <v>6</v>
+      </c>
+      <c r="G9" s="57">
+        <v>6</v>
+      </c>
+      <c r="H9" s="57">
+        <v>15</v>
+      </c>
+      <c r="I9" s="57">
+        <v>12</v>
+      </c>
+      <c r="J9" s="57">
+        <v>15</v>
+      </c>
+      <c r="K9" s="57">
+        <v>20</v>
+      </c>
+      <c r="L9" s="57"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="9">
+        <f>SUM(C9:K9)</f>
+        <v>92</v>
+      </c>
+      <c r="O9" s="2"/>
+      <c r="R9" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="S9" s="12">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="T9" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="U9" s="5">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="str">
+        <f>Marksheet!A9</f>
+        <v>Deevija Garg</v>
+      </c>
+      <c r="B10" s="14">
+        <f>Marksheet!B9</f>
+        <v>590013559</v>
+      </c>
+      <c r="C10" s="57">
+        <v>6</v>
+      </c>
+      <c r="D10" s="57">
+        <v>5</v>
+      </c>
+      <c r="E10" s="57">
+        <v>5</v>
+      </c>
+      <c r="F10" s="57">
+        <v>6</v>
+      </c>
+      <c r="G10" s="57">
+        <v>6</v>
+      </c>
+      <c r="H10" s="57">
+        <v>13</v>
+      </c>
+      <c r="I10" s="57">
+        <v>3</v>
+      </c>
+      <c r="J10" s="57">
+        <v>12</v>
+      </c>
+      <c r="K10" s="57">
+        <v>5</v>
+      </c>
+      <c r="L10" s="57"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="9">
+        <f>SUM(C10:K10)</f>
+        <v>61</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="R10" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="S10" s="12">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="T10" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="U10" s="5">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="4"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="str">
+        <f>Marksheet!A10</f>
+        <v>Chandni Negi</v>
+      </c>
+      <c r="B11" s="14">
+        <f>Marksheet!B10</f>
+        <v>590014314</v>
+      </c>
+      <c r="C11" s="58">
+        <v>6</v>
+      </c>
+      <c r="D11" s="58">
+        <v>6</v>
+      </c>
+      <c r="E11" s="58">
+        <v>6</v>
+      </c>
+      <c r="F11" s="58">
+        <v>4</v>
+      </c>
+      <c r="G11" s="58">
+        <v>4</v>
+      </c>
+      <c r="H11" s="58">
+        <v>15</v>
+      </c>
+      <c r="I11" s="57">
+        <v>15</v>
+      </c>
+      <c r="J11" s="57">
+        <v>10</v>
+      </c>
+      <c r="K11" s="57">
+        <v>10</v>
+      </c>
+      <c r="L11" s="57"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="9">
+        <f>SUM(C11:K11)</f>
+        <v>76</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="R11" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="S11" s="12">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="T11" s="5">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="U11" s="5">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="4"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="str">
+        <f>Marksheet!A11</f>
+        <v>Divya Krishna</v>
+      </c>
+      <c r="B12" s="14">
+        <f>Marksheet!B11</f>
+        <v>590016280</v>
+      </c>
+      <c r="C12" s="57">
+        <v>6</v>
+      </c>
+      <c r="D12" s="57">
+        <v>6</v>
+      </c>
+      <c r="E12" s="57">
+        <v>4</v>
+      </c>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57">
+        <v>6</v>
+      </c>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57">
+        <v>7</v>
+      </c>
+      <c r="J12" s="57">
+        <v>6</v>
+      </c>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="9">
+        <f>SUM(C12:J12)</f>
+        <v>35</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="R12" s="12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="S12" s="12">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="T12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="str">
+        <f>Marksheet!A12</f>
+        <v>Shubhangee Shukla</v>
+      </c>
+      <c r="B13" s="14">
+        <f>Marksheet!B12</f>
+        <v>590017181</v>
+      </c>
+      <c r="C13" s="57">
+        <v>6</v>
+      </c>
+      <c r="D13" s="57">
+        <v>3</v>
+      </c>
+      <c r="E13" s="57">
+        <v>5</v>
+      </c>
+      <c r="F13" s="57">
+        <v>3</v>
+      </c>
+      <c r="G13" s="57">
+        <v>4</v>
+      </c>
+      <c r="H13" s="57">
+        <v>5</v>
+      </c>
+      <c r="I13" s="57">
+        <v>0</v>
+      </c>
+      <c r="J13" s="57">
+        <v>4</v>
+      </c>
+      <c r="K13" s="57">
+        <v>0</v>
+      </c>
+      <c r="L13" s="57"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="9">
+        <f>SUM(C13:K13)</f>
+        <v>30</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="R13" s="12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="S13" s="12">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="T13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="str">
+        <f>Marksheet!A13</f>
+        <v>Heera Singh</v>
+      </c>
+      <c r="B14" s="14">
+        <f>Marksheet!B13</f>
+        <v>590017658</v>
+      </c>
+      <c r="C14" s="57">
+        <v>6</v>
+      </c>
+      <c r="D14" s="57">
+        <v>5</v>
+      </c>
+      <c r="E14" s="57">
+        <v>6</v>
+      </c>
+      <c r="F14" s="57">
+        <v>4</v>
+      </c>
+      <c r="G14" s="57">
+        <v>4</v>
+      </c>
+      <c r="H14" s="57">
+        <v>10</v>
+      </c>
+      <c r="I14" s="57">
+        <v>5</v>
+      </c>
+      <c r="J14" s="57">
+        <v>7</v>
+      </c>
+      <c r="K14" s="57">
+        <v>0</v>
+      </c>
+      <c r="L14" s="57"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="9">
+        <f>SUM(C14:K14)</f>
+        <v>47</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="R14" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="S14" s="12">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="T14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="str">
+        <f>Marksheet!A14</f>
+        <v>Abhineet Srivastava</v>
+      </c>
+      <c r="B15" s="14">
+        <f>Marksheet!B14</f>
+        <v>590017776</v>
+      </c>
+      <c r="C15" s="57">
+        <v>6</v>
+      </c>
+      <c r="D15" s="57">
+        <v>6</v>
+      </c>
+      <c r="E15" s="57">
+        <v>6</v>
+      </c>
+      <c r="F15" s="57">
+        <v>5</v>
+      </c>
+      <c r="G15" s="57">
+        <v>6</v>
+      </c>
+      <c r="H15" s="57">
+        <v>13</v>
+      </c>
+      <c r="I15" s="57">
+        <v>15</v>
+      </c>
+      <c r="J15" s="57">
+        <v>15</v>
+      </c>
+      <c r="K15" s="57">
+        <v>20</v>
+      </c>
+      <c r="L15" s="57"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="9">
+        <f>SUM(C15:K15)</f>
+        <v>92</v>
+      </c>
+      <c r="O15" s="2"/>
+      <c r="R15" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="S15" s="12">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="T15" s="5">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="U15" s="5">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="4"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="str">
+        <f>Marksheet!A15</f>
+        <v>Tanisha Chanani</v>
+      </c>
+      <c r="B16" s="14">
+        <f>Marksheet!B15</f>
+        <v>590018198</v>
+      </c>
+      <c r="C16" s="57">
+        <v>6</v>
+      </c>
+      <c r="D16" s="57">
+        <v>5</v>
+      </c>
+      <c r="E16" s="57">
+        <v>6</v>
+      </c>
+      <c r="F16" s="57">
+        <v>6</v>
+      </c>
+      <c r="G16" s="57">
+        <v>4</v>
+      </c>
+      <c r="H16" s="57">
+        <v>14</v>
+      </c>
+      <c r="I16" s="57">
+        <v>15</v>
+      </c>
+      <c r="J16" s="57">
+        <v>15</v>
+      </c>
+      <c r="K16" s="57">
+        <v>15</v>
+      </c>
+      <c r="L16" s="57"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="9">
+        <f>SUM(C16:K16)</f>
+        <v>86</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="R16" s="12">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="S16" s="12">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="T16" s="5">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="U16" s="5">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="4"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="str">
+        <f>Marksheet!A16</f>
+        <v>Rushil Soni</v>
+      </c>
+      <c r="B17" s="14">
+        <f>Marksheet!B16</f>
+        <v>590018519</v>
+      </c>
+      <c r="C17" s="57">
+        <v>5</v>
+      </c>
+      <c r="D17" s="57">
+        <v>4</v>
+      </c>
+      <c r="E17" s="57">
+        <v>3</v>
+      </c>
+      <c r="F17" s="57">
+        <v>1</v>
+      </c>
+      <c r="G17" s="57">
+        <v>4</v>
+      </c>
+      <c r="H17" s="57">
+        <v>2</v>
+      </c>
+      <c r="I17" s="57">
+        <v>4</v>
+      </c>
+      <c r="J17" s="57">
+        <v>4</v>
+      </c>
+      <c r="K17" s="57">
+        <v>5</v>
+      </c>
+      <c r="L17" s="57"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="9">
+        <f>SUM(C17:K17)</f>
+        <v>32</v>
+      </c>
+      <c r="O17" s="2"/>
+      <c r="R17" s="12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="S17" s="12">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="T17" s="5">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="U17" s="5">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="2"/>
+      <c r="R18" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="2"/>
+      <c r="R19" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="2"/>
+      <c r="R20" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="10"/>
+      <c r="R21" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="30"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="30"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="30"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="30"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="30"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="30"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="30"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="30"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="30"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="30"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="30"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="30"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="30"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFC0182-6626-4C28-AE12-3805CD8061D9}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6115,134 +7042,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>5</v>
@@ -6625,7 +7552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D596BA-28B6-4E3D-B4DD-BA2BE95F4450}">
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6638,134 +7565,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>5</v>
@@ -7148,7 +8075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3EC6E4-73FE-451F-9DA1-2F8671C4541C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7164,134 +8091,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -7663,618 +8590,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355320EC-5887-4CA4-8B00-C82693C60F77}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" style="13" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-    </row>
-    <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
-        <f>Marksheet!A2</f>
-        <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
-      </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="9">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9">
-        <v>5</v>
-      </c>
-      <c r="F5" s="9">
-        <v>5</v>
-      </c>
-      <c r="G5" s="9">
-        <v>15</v>
-      </c>
-      <c r="H5" s="9">
-        <v>15</v>
-      </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9">
-        <f>SUM(C5:H5)</f>
-        <v>50</v>
-      </c>
-      <c r="O5" s="9"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="str">
-        <f>Marksheet!A5</f>
-        <v>Vansh Sharma</v>
-      </c>
-      <c r="B6" s="14">
-        <f>Marksheet!B5</f>
-        <v>590010833</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="9">
-        <f t="shared" ref="N6:N21" si="0">SUM(C6:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="str">
-        <f>Marksheet!A6</f>
-        <v>Mokshika Saini</v>
-      </c>
-      <c r="B7" s="14">
-        <f>Marksheet!B6</f>
-        <v>590010853</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="str">
-        <f>Marksheet!A7</f>
-        <v>Sakshi Sheshrao Charde</v>
-      </c>
-      <c r="B8" s="14">
-        <f>Marksheet!B7</f>
-        <v>590011314</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="str">
-        <f>Marksheet!A8</f>
-        <v>Akash Vinodshirke</v>
-      </c>
-      <c r="B9" s="14">
-        <f>Marksheet!B8</f>
-        <v>590011462</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="str">
-        <f>Marksheet!A9</f>
-        <v>Deevija Garg</v>
-      </c>
-      <c r="B10" s="14">
-        <f>Marksheet!B9</f>
-        <v>590013559</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="str">
-        <f>Marksheet!A10</f>
-        <v>Chandni Negi</v>
-      </c>
-      <c r="B11" s="14">
-        <f>Marksheet!B10</f>
-        <v>590014314</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="2"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="str">
-        <f>Marksheet!A11</f>
-        <v>Divya Krishna</v>
-      </c>
-      <c r="B12" s="14">
-        <f>Marksheet!B11</f>
-        <v>590016280</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="str">
-        <f>Marksheet!A12</f>
-        <v>Shubhangee Shukla</v>
-      </c>
-      <c r="B13" s="14">
-        <f>Marksheet!B12</f>
-        <v>590017181</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="str">
-        <f>Marksheet!A13</f>
-        <v>Heera Singh</v>
-      </c>
-      <c r="B14" s="14">
-        <f>Marksheet!B13</f>
-        <v>590017658</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="2"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="str">
-        <f>Marksheet!A14</f>
-        <v>Abhineet Srivastava</v>
-      </c>
-      <c r="B15" s="14">
-        <f>Marksheet!B14</f>
-        <v>590017776</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="str">
-        <f>Marksheet!A15</f>
-        <v>Tanisha Chanani</v>
-      </c>
-      <c r="B16" s="14">
-        <f>Marksheet!B15</f>
-        <v>590018198</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="str">
-        <f>Marksheet!A16</f>
-        <v>Rushil Soni</v>
-      </c>
-      <c r="B17" s="14">
-        <f>Marksheet!B16</f>
-        <v>590018519</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="31"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="31"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="31"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="31"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="31"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="31"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="31"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="31"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="31"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="31"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="31"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="31"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="31"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146A9C77-33C1-4CBC-91FC-1994BECB7B48}">
   <sheetPr>
@@ -8283,140 +8598,140 @@
   <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="22" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
     <col min="15" max="15" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A1" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
+      <c r="A1" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
     </row>
     <row r="2" spans="1:15" ht="24.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="56" t="str">
+      <c r="A2" s="52" t="str">
         <f>Marksheet!A2</f>
         <v xml:space="preserve">Computatioal Astrophysics (PHYS 8202) </v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="19"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -8458,7 +8773,7 @@
       <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
+      <c r="A6" s="21">
         <f>'Mid Sem'!B6</f>
         <v>590010833</v>
       </c>
@@ -8481,7 +8796,7 @@
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <f>'Mid Sem'!B7</f>
         <v>590010853</v>
       </c>
@@ -8504,7 +8819,7 @@
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
+      <c r="A8" s="21">
         <f>'Mid Sem'!B8</f>
         <v>590011314</v>
       </c>
@@ -8527,7 +8842,7 @@
       <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
+      <c r="A9" s="21">
         <f>'Mid Sem'!B9</f>
         <v>590011462</v>
       </c>
@@ -8550,7 +8865,7 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <f>'Mid Sem'!B10</f>
         <v>590013559</v>
       </c>
@@ -8573,7 +8888,7 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
+      <c r="A11" s="21">
         <f>'Mid Sem'!B11</f>
         <v>590014314</v>
       </c>
@@ -8596,7 +8911,7 @@
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="21">
         <f>'Mid Sem'!B12</f>
         <v>590016280</v>
       </c>
@@ -8619,7 +8934,7 @@
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
+      <c r="A13" s="21">
         <f>'Mid Sem'!B13</f>
         <v>590017181</v>
       </c>
@@ -8642,7 +8957,7 @@
       <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
+      <c r="A14" s="21">
         <f>'Mid Sem'!B14</f>
         <v>590017658</v>
       </c>
@@ -8665,7 +8980,7 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <f>'Mid Sem'!B15</f>
         <v>590017776</v>
       </c>
@@ -8688,7 +9003,7 @@
       <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+      <c r="A16" s="21">
         <f>'Mid Sem'!B16</f>
         <v>590018198</v>
       </c>
@@ -8711,7 +9026,7 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="22">
+      <c r="A17" s="21">
         <f>'Mid Sem'!B17</f>
         <v>590018519</v>
       </c>
@@ -8734,7 +9049,7 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="5"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -8751,7 +9066,7 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="5"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -8768,7 +9083,7 @@
       <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="5"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -8785,7 +9100,7 @@
       <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="5"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -8802,7 +9117,7 @@
       <c r="O21" s="2"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="5"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>

--- a/resources/Marks/2026/even/Computational Astrophysics.xlsx
+++ b/resources/Marks/2026/even/Computational Astrophysics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gusindia01-my.sharepoint.com/personal/nitesh_kumar_ddn_upes_ac_in/Documents/UPES/2026/Jan-May-2026/Computational Astrophysics/Marks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2058" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FB3EC6B-031A-4AA7-AE7C-9AF0D47AD5B4}"/>
+  <xr:revisionPtr revIDLastSave="2063" documentId="11_3FC952BF37FB7C428065D6D94F732ED04C5A5A3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27B6FA7B-2E65-422C-8848-847569281BAE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="553" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Marksheet" sheetId="2" r:id="rId1"/>
@@ -551,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -710,6 +710,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1225,13 +1228,19 @@
         <f t="shared" ref="K5:K16" si="1">J5/2</f>
         <v>18.2</v>
       </c>
-      <c r="L5" s="28"/>
-      <c r="M5" s="17"/>
+      <c r="L5" s="59">
+        <f t="shared" ref="L5:L16" si="2">M5/5</f>
+        <v>8.4</v>
+      </c>
+      <c r="M5" s="17">
+        <f>'Mid Sem'!N6</f>
+        <v>42</v>
+      </c>
       <c r="N5" s="17"/>
       <c r="O5" s="28"/>
       <c r="P5" s="5">
-        <f t="shared" ref="P5:P16" si="2">SUM(K5,L5,O5)</f>
-        <v>18.2</v>
+        <f t="shared" ref="P5:P16" si="3">SUM(K5,L5,O5)</f>
+        <v>26.6</v>
       </c>
       <c r="Q5" s="34"/>
       <c r="S5" s="26" t="s">
@@ -1272,12 +1281,18 @@
         <f t="shared" si="1"/>
         <v>15.4</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="17"/>
+      <c r="L6" s="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="17">
+        <f>'Mid Sem'!N7</f>
+        <v>0</v>
+      </c>
       <c r="N6" s="17"/>
       <c r="O6" s="28"/>
       <c r="P6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15.4</v>
       </c>
       <c r="Q6" s="34"/>
@@ -1319,13 +1334,19 @@
         <f t="shared" si="1"/>
         <v>22.700000000000003</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="17"/>
+      <c r="L7" s="59">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="M7" s="17">
+        <f>'Mid Sem'!N8</f>
+        <v>40</v>
+      </c>
       <c r="N7" s="17"/>
       <c r="O7" s="28"/>
       <c r="P7" s="5">
-        <f t="shared" si="2"/>
-        <v>22.700000000000003</v>
+        <f t="shared" si="3"/>
+        <v>30.700000000000003</v>
       </c>
       <c r="Q7" s="34"/>
       <c r="S7" s="26" t="s">
@@ -1366,13 +1387,19 @@
         <f t="shared" si="1"/>
         <v>24.2</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="17"/>
+      <c r="L8" s="59">
+        <f t="shared" si="2"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M8" s="17">
+        <f>'Mid Sem'!N9</f>
+        <v>92</v>
+      </c>
       <c r="N8" s="17"/>
       <c r="O8" s="28"/>
       <c r="P8" s="5">
-        <f t="shared" si="2"/>
-        <v>24.2</v>
+        <f t="shared" si="3"/>
+        <v>42.599999999999994</v>
       </c>
       <c r="Q8" s="34"/>
       <c r="S8" s="26" t="s">
@@ -1413,13 +1440,19 @@
         <f t="shared" si="1"/>
         <v>18.05</v>
       </c>
-      <c r="L9" s="28"/>
-      <c r="M9" s="17"/>
+      <c r="L9" s="59">
+        <f t="shared" si="2"/>
+        <v>12.2</v>
+      </c>
+      <c r="M9" s="17">
+        <f>'Mid Sem'!N10</f>
+        <v>61</v>
+      </c>
       <c r="N9" s="17"/>
       <c r="O9" s="28"/>
       <c r="P9" s="5">
-        <f t="shared" si="2"/>
-        <v>18.05</v>
+        <f t="shared" si="3"/>
+        <v>30.25</v>
       </c>
       <c r="Q9" s="34"/>
       <c r="S9" s="26" t="s">
@@ -1460,13 +1493,19 @@
         <f t="shared" si="1"/>
         <v>23.5</v>
       </c>
-      <c r="L10" s="28"/>
-      <c r="M10" s="17"/>
+      <c r="L10" s="59">
+        <f t="shared" si="2"/>
+        <v>15.2</v>
+      </c>
+      <c r="M10" s="17">
+        <f>'Mid Sem'!N11</f>
+        <v>76</v>
+      </c>
       <c r="N10" s="17"/>
       <c r="O10" s="28"/>
       <c r="P10" s="5">
-        <f t="shared" si="2"/>
-        <v>23.5</v>
+        <f t="shared" si="3"/>
+        <v>38.700000000000003</v>
       </c>
       <c r="Q10" s="34"/>
       <c r="S10" s="26" t="s">
@@ -1507,13 +1546,19 @@
         <f t="shared" si="1"/>
         <v>5.25</v>
       </c>
-      <c r="L11" s="28"/>
-      <c r="M11" s="17"/>
+      <c r="L11" s="59">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="M11" s="17">
+        <f>'Mid Sem'!N12</f>
+        <v>35</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="28"/>
       <c r="P11" s="5">
-        <f t="shared" si="2"/>
-        <v>5.25</v>
+        <f t="shared" si="3"/>
+        <v>12.25</v>
       </c>
       <c r="Q11" s="34"/>
       <c r="S11" s="26" t="s">
@@ -1554,13 +1599,19 @@
         <f t="shared" si="1"/>
         <v>12.6</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="17"/>
+      <c r="L12" s="59">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="M12" s="17">
+        <f>'Mid Sem'!N13</f>
+        <v>30</v>
+      </c>
       <c r="N12" s="17"/>
       <c r="O12" s="28"/>
       <c r="P12" s="5">
-        <f t="shared" si="2"/>
-        <v>12.6</v>
+        <f t="shared" si="3"/>
+        <v>18.600000000000001</v>
       </c>
       <c r="Q12" s="34"/>
       <c r="S12" s="26" t="s">
@@ -1601,13 +1652,19 @@
         <f t="shared" si="1"/>
         <v>18.25</v>
       </c>
-      <c r="L13" s="28"/>
-      <c r="M13" s="17"/>
+      <c r="L13" s="59">
+        <f t="shared" si="2"/>
+        <v>9.4</v>
+      </c>
+      <c r="M13" s="17">
+        <f>'Mid Sem'!N14</f>
+        <v>47</v>
+      </c>
       <c r="N13" s="17"/>
       <c r="O13" s="28"/>
       <c r="P13" s="5">
-        <f t="shared" si="2"/>
-        <v>18.25</v>
+        <f t="shared" si="3"/>
+        <v>27.65</v>
       </c>
       <c r="Q13" s="34"/>
       <c r="S13" s="26" t="s">
@@ -1648,13 +1705,19 @@
         <f t="shared" si="1"/>
         <v>23.675000000000001</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="17"/>
+      <c r="L14" s="59">
+        <f t="shared" si="2"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M14" s="17">
+        <f>'Mid Sem'!N15</f>
+        <v>92</v>
+      </c>
       <c r="N14" s="17"/>
       <c r="O14" s="28"/>
       <c r="P14" s="5">
-        <f t="shared" si="2"/>
-        <v>23.675000000000001</v>
+        <f t="shared" si="3"/>
+        <v>42.075000000000003</v>
       </c>
       <c r="Q14" s="34"/>
       <c r="S14" s="26" t="s">
@@ -1695,13 +1758,19 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="L15" s="28"/>
-      <c r="M15" s="17"/>
+      <c r="L15" s="59">
+        <f t="shared" si="2"/>
+        <v>17.2</v>
+      </c>
+      <c r="M15" s="17">
+        <f>'Mid Sem'!N16</f>
+        <v>86</v>
+      </c>
       <c r="N15" s="17"/>
       <c r="O15" s="28"/>
       <c r="P15" s="5">
-        <f t="shared" si="2"/>
-        <v>24</v>
+        <f t="shared" si="3"/>
+        <v>41.2</v>
       </c>
       <c r="Q15" s="34"/>
       <c r="S15" s="26" t="s">
@@ -1742,13 +1811,19 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L16" s="28"/>
-      <c r="M16" s="17"/>
+      <c r="L16" s="59">
+        <f t="shared" si="2"/>
+        <v>6.4</v>
+      </c>
+      <c r="M16" s="17">
+        <f>'Mid Sem'!N17</f>
+        <v>32</v>
+      </c>
       <c r="N16" s="17"/>
       <c r="O16" s="28"/>
       <c r="P16" s="5">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>26.4</v>
       </c>
       <c r="Q16" s="34"/>
       <c r="S16" s="26" t="s">
@@ -1777,7 +1852,7 @@
       <c r="P17" s="42"/>
       <c r="Q17" s="43"/>
       <c r="U17" t="str">
-        <f t="shared" ref="U17" si="3">LOWER(S17)</f>
+        <f t="shared" ref="U17" si="4">LOWER(S17)</f>
         <v/>
       </c>
     </row>
@@ -1827,11 +1902,11 @@
         <v>14.9</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:F20" si="4">MAX(E5:E16)</f>
+        <f t="shared" ref="E20:F20" si="5">MAX(E5:E16)</f>
         <v>14.700000000000001</v>
       </c>
       <c r="F20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="G20" s="25"/>
@@ -1854,11 +1929,11 @@
         <v>13.7</v>
       </c>
       <c r="E21">
-        <f t="shared" ref="E21:F21" si="5">_xlfn.MINIFS(E5:E16,E5:E16, "&gt;0")</f>
+        <f t="shared" ref="E21:F21" si="6">_xlfn.MINIFS(E5:E16,E5:E16, "&gt;0")</f>
         <v>6</v>
       </c>
       <c r="F21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
     </row>
@@ -1871,11 +1946,11 @@
         <v>14.5</v>
       </c>
       <c r="E22">
-        <f t="shared" ref="E22:F22" si="6">MEDIAN(E5:E16)</f>
+        <f t="shared" ref="E22:F22" si="7">MEDIAN(E5:E16)</f>
         <v>13.200000000000001</v>
       </c>
       <c r="F22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
     </row>
